--- a/data/estoque_inicial.xlsx
+++ b/data/estoque_inicial.xlsx
@@ -1,65 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matheus\estancia_dos_ventos\ambiente_virtual\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD28D070-1CD5-4936-95CD-3FFE71BDEE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2325" windowWidth="16995" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>produto</t>
-  </si>
-  <si>
-    <t>quantidade_disponivel</t>
-  </si>
-  <si>
-    <t>unidade</t>
-  </si>
-  <si>
-    <t>preco</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -74,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -398,28 +420,4344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E206"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>preco</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>quantidade_embalagem</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unidade</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>quantidade_disponivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. bol para creme 500ml</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. bolo g35m (galvonotek)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. cartao agradecimento</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>190</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. etiqueta circunferencia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. etiqueta validade</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>225</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. forma de pudim e pizza</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1. isopor pizza</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. lacre sacola</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>240</v>
+      </c>
+      <c r="C9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1. mimo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1. mimo doce</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1. pote 1.000ml para massas</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1. pote 500ml para marmitas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1. pote para creme</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1. pote para forno g240 (fundo preto)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>172</v>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1. pote para fricasse</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>23</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. pote para molho de 200 gramas</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1. saco pardo (embalar marmitas)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>128</v>
+      </c>
+      <c r="C18" t="n">
+        <v>500</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1. sacola com logo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1. sanduicheira</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1. saquinho para marmitas</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>abacate</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>abobrinha</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aborinha</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>acafrao</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>acucar cristal</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>acucar demerara</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>acucar uniao</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>agua de coco</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aipim</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>al pesto</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" t="n">
+        <v>180</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>alcaparras</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="C32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>alface</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>alho poro</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>almondegas com moho</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>amendoa</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>amendoim</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>400</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>arroz arboreo</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>arroz branco cozido</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>arroz cozido colorido</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>arroz cozido polverizado</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>arroz integral</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>arroz intgral cozido</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>45</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>arroz polverizado</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>28</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>aspargos</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>22</v>
+      </c>
+      <c r="C45" t="n">
+        <v>185</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aveia em flocos</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>azeite de oliva</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>36</v>
+      </c>
+      <c r="C47" t="n">
+        <v>500</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>azeite girasol ou canola</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>azeite spray para formas</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>azeitona sem coroco</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>100</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bacon</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>70</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>batata doce</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>batata inglesa</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>batata palha</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>batata pequena</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>9</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bergamota</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>beterraba</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>brocolis</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>500</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>caldo de legumes</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>carne de panela</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>25</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>carne moida</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>130</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>carne para bife</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>35</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>carne suina</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>castanha caju</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>85</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>castanha do para</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>85</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cebola</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cenoura</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cenoura cozida</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>champinhon em conserva</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>300</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>chocolate do frei 50%</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>23</v>
+      </c>
+      <c r="C71" t="n">
+        <v>200</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>chocolate em po (50%)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>17</v>
+      </c>
+      <c r="C72" t="n">
+        <v>200</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>chuchu</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>coco ralado</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C74" t="n">
+        <v>100</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>coco seco</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>115</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>costelinha de porco</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>24</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>costelinha defumada</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>couve folha</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>couve-flor</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>500</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>couve-flor cozida</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>35</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>crean cheese</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>creme de leite</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>damasco</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>79</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>embalagem para bolo g32 galvonotek</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>enfeite para bolo</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>enlatado ervilha com milho</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>170</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>entreco carne</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>60</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ervilha congelada</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C88" t="n">
+        <v>300</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>espaguete paganini/parafuso</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>13</v>
+      </c>
+      <c r="C89" t="n">
+        <v>500</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>espinafre</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>farelo de aveia</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C91" t="n">
+        <v>170</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>farinha de amendoas</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>farinha de arroz</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>25</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>farinha de milho</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>farinha de milho flocada</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>farinha de rosca</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>8</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>farinha de trigo</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>19</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>farinha massa</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>23</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>feijao cozido</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>feijao preto</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>feijao vermelho</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" t="n">
+        <v>500</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>feijao vermelho</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" t="n">
+        <v>500</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>figo fruta</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>fijoada</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>10</v>
+      </c>
+      <c r="C104" t="n">
+        <v>420</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>folha de aluminio</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>frango grelhado</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>61</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>funghi</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>119</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>gelatina zero</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>gengibre</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>goiabada</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>300</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>gorgonzola</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>70</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>grao de bico</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>7</v>
+      </c>
+      <c r="C112" t="n">
+        <v>380</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>guisado</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>30</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>guisado pronto cozido</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>27</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>iogurte de cenoura</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="n">
+        <v>170</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>iogurte natural</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>170</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ktchup heinz</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>12</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>laranja suco</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>leite</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>leite condensado</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C120" t="n">
+        <v>395</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>leite em po</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>24</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>lentilha</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C122" t="n">
+        <v>400</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>lentilha pronta</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>limao</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>limao siciliano</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>linguica calabresa</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>42</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>maca</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>macarrao</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="C128" t="n">
+        <v>500</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>maizena</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>20</v>
+      </c>
+      <c r="C129" t="n">
+        <v>720</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>mamao papaia</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>10</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>manteiga</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>12</v>
+      </c>
+      <c r="C132" t="n">
+        <v>200</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>maracuja fruta</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>23</v>
+      </c>
+      <c r="C133" t="n">
+        <v>275</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>margarina</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" t="n">
+        <v>500</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>massa conchinha</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C135" t="n">
+        <v>500</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>massa de pastel em rolo</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>33</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>massa de tomate</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" t="n">
+        <v>300</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>massa para lasanha</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>5</v>
+      </c>
+      <c r="C138" t="n">
+        <v>500</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>massa para pastel</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>7</v>
+      </c>
+      <c r="C139" t="n">
+        <v>500</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>massa penne sem gluten</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="C140" t="n">
+        <v>300</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>massa rigatoni</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" t="n">
+        <v>500</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>matambre</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>43</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>matambre</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>43</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>mel</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>20</v>
+      </c>
+      <c r="C144" t="n">
+        <v>290</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>melancia</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>merengue pequenino decorativo</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>12</v>
+      </c>
+      <c r="C146" t="n">
+        <v>150</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>milho enlatado</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="n">
+        <v>170</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>mix de farinha s/gluten</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>molho branco de caixinha</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" t="n">
+        <v>200</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>molho branco pronto</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>35</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>molho de frango</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="n">
+        <v>100</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>molho madeira</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C152" t="n">
+        <v>200</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>molho vermelho pronto</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>17</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>moranga</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>moranguinho</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>31</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>mostarda</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>9</v>
+      </c>
+      <c r="C156" t="n">
+        <v>200</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>nata</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>11</v>
+      </c>
+      <c r="C157" t="n">
+        <v>300</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>nhoque</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>10</v>
+      </c>
+      <c r="C158" t="n">
+        <v>500</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>nozes</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>83</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ortela</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C160" t="n">
+        <v>16</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ovo codorna</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>7</v>
+      </c>
+      <c r="C161" t="n">
+        <v>130</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ovos</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>12</v>
+      </c>
+      <c r="C162" t="n">
+        <v>20</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>palmito selenza</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>20</v>
+      </c>
+      <c r="C163" t="n">
+        <v>300</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>pao colonial sanduiche natural</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>20</v>
+      </c>
+      <c r="C164" t="n">
+        <v>450</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>patinho bife</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>40</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>peito de frango</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>20</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>pepino em conserva taua</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="C167" t="n">
+        <v>300</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>pepino japones</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>15</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>pimenta</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>20</v>
+      </c>
+      <c r="C169" t="n">
+        <v>50</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>pimentao colorido</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>30</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>pimentao verde</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>polentina</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="n">
+        <v>500</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>polvilho doce</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>9</v>
+      </c>
+      <c r="C173" t="n">
+        <v>500</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pote para biscoitos/sucrilhos</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>15</v>
+      </c>
+      <c r="C174" t="n">
+        <v>10</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>presunto cozido sadia</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C175" t="n">
+        <v>200</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>presunto para picadinho</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>51</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>queijo para picadinho</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>45</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>queijo prato</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>18</v>
+      </c>
+      <c r="C178" t="n">
+        <v>400</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>queijo ralado</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>70</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>requeijao</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>6</v>
+      </c>
+      <c r="C180" t="n">
+        <v>180</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ricota</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="C181" t="n">
+        <v>256</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>roma</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>70</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>royal</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>15</v>
+      </c>
+      <c r="C183" t="n">
+        <v>250</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>rucula</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>saco para sucrilhos</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>10</v>
+      </c>
+      <c r="C185" t="n">
+        <v>100</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>sal cisne</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>salame fatiado</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>58</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>salsinha</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>4</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>sardinha</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>6</v>
+      </c>
+      <c r="C189" t="n">
+        <v>125</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>sobrecoxa assada</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>68</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>sobrecoxa de frango</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>11</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>suco de laranja</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>500</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>suco de maracuja</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>8</v>
+      </c>
+      <c r="C193" t="n">
+        <v>500</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>suco de maracuja</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>13</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tempero verde</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>13</v>
+      </c>
+      <c r="C195" t="n">
+        <v>450</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tomate</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>8</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tomate cereja</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" t="n">
+        <v>180</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tomate seco</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>17</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tortei</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>14</v>
+      </c>
+      <c r="C199" t="n">
+        <v>500</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tripada</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>25</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tulipa da asa</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tulipinha</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>xantana</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>49</v>
+      </c>
+      <c r="C203" t="n">
+        <v>100</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>batata doces</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>8</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>[teste] - peito de frango</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>26</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>[teste] feijao branco</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/estoque_inicial.xlsx
+++ b/data/estoque_inicial.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">

--- a/data/estoque_inicial.xlsx
+++ b/data/estoque_inicial.xlsx
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="40">

--- a/data/estoque_inicial.xlsx
+++ b/data/estoque_inicial.xlsx
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103">
